--- a/testData/testData.xlsx
+++ b/testData/testData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\eclipse projects\NewAutomation\OpenKartSeleniumProject\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476635BC-3CAF-4450-88CD-B1CB3BE7A266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1607B73-7723-437D-8829-A24BF77749E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t>Web Url</t>
   </si>
@@ -80,12 +80,6 @@
   </si>
   <si>
     <t>Platform</t>
-  </si>
-  <si>
-    <t>Linux</t>
-  </si>
-  <si>
-    <t>Remote</t>
   </si>
 </sst>
 </file>
@@ -458,16 +452,10 @@
       <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
